--- a/data/trans_orig/IP07C04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C04-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32370</t>
+          <t>32570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42940</t>
+          <t>43643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42954</t>
+          <t>43559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54848</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80240</t>
+          <t>80306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96730</t>
+          <t>96207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39406</t>
+          <t>39258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58967</t>
+          <t>59335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73825</t>
+          <t>72950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54463</t>
+          <t>54811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69143</t>
+          <t>69103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117618</t>
+          <t>119044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137534</t>
+          <t>139031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34775</t>
+          <t>34372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32170</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>61867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -1640,47 +1640,47 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>1302</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7797</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40223</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60820</t>
+          <t>60351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76997</t>
+          <t>77122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30421</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37006</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>53066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>482</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52437</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65298</t>
+          <t>64752</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92445</t>
+          <t>93463</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113356</t>
+          <t>113929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20969</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>35091</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33660</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63402</t>
+          <t>64019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170150</t>
+          <t>170576</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196528</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190615</t>
+          <t>190652</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>218211</t>
+          <t>216814</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>370417</t>
+          <t>369016</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>406483</t>
+          <t>407370</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>105345</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>79270</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105381</t>
+          <t>105305</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>166387</t>
+          <t>165532</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>200674</t>
+          <t>203662</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30962</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>44055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52086</t>
+          <t>52028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73866</t>
+          <t>72819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92880</t>
+          <t>92338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>28464</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35809</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54707</t>
+          <t>55274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>56805</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71413</t>
+          <t>70985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>46986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61890</t>
+          <t>62008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107681</t>
+          <t>108356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129810</t>
+          <t>129599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>36984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>29352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44880</t>
+          <t>44465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56316</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77750</t>
+          <t>77374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27450</t>
+          <t>27573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40753</t>
+          <t>40612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>40661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53070</t>
+          <t>52673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>72385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89221</t>
+          <t>90599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>34456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>56487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>43196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59036</t>
+          <t>59743</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84958</t>
+          <t>85216</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108155</t>
+          <t>108349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,71%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28284</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44096</t>
+          <t>44351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58559</t>
+          <t>58607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81387</t>
+          <t>81509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>166874</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>196520</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>184999</t>
+          <t>184673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>214121</t>
+          <t>213243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>360633</t>
+          <t>360857</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>401399</t>
+          <t>399760</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>101589</t>
+          <t>102227</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>129609</t>
+          <t>129177</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>100156</t>
+          <t>100268</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>127306</t>
+          <t>127819</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>209276</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>249816</t>
+          <t>248068</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51078</t>
+          <t>51228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>35803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50172</t>
+          <t>50901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77980</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97290</t>
+          <t>97109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>28827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>32131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>37559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>48320</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65109</t>
+          <t>64473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56013</t>
+          <t>55651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71887</t>
+          <t>71457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108792</t>
+          <t>108860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131495</t>
+          <t>132076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29724</t>
+          <t>29832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>45659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>30147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>46121</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64016</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86196</t>
+          <t>85945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16852</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39953</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52158</t>
+          <t>52384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55372</t>
+          <t>54894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85153</t>
+          <t>84631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104767</t>
+          <t>104275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>28222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31267</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54850</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47363</t>
+          <t>46531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65136</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47599</t>
+          <t>47244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64421</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100429</t>
+          <t>99990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124762</t>
+          <t>123731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,83%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35878</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53849</t>
+          <t>53870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47659</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>73902</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>96077</t>
+          <t>97274</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>190271</t>
+          <t>190265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>220194</t>
+          <t>221744</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>195433</t>
+          <t>195551</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>228045</t>
+          <t>226418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>397743</t>
+          <t>393387</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>438420</t>
+          <t>437515</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>109131</t>
+          <t>109274</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139562</t>
+          <t>138798</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110181</t>
+          <t>112032</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>141961</t>
+          <t>140237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230910</t>
+          <t>229674</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>270385</t>
+          <t>273356</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
